--- a/output/pdf_financials_xlsx/GNG.xlsx
+++ b/output/pdf_financials_xlsx/GNG.xlsx
@@ -4690,31 +4690,31 @@
         <v>0</v>
       </c>
       <c r="E92" s="3" t="n">
-        <v>0</v>
+        <v>2.98677</v>
       </c>
       <c r="F92" s="3" t="n">
-        <v>0</v>
+        <v>2.98677</v>
       </c>
       <c r="G92" s="3" t="n">
-        <v>0</v>
+        <v>3.066151</v>
       </c>
       <c r="H92" s="3" t="n">
-        <v>0</v>
+        <v>3.068546</v>
       </c>
       <c r="I92" s="3" t="n">
-        <v>0</v>
+        <v>3.298267</v>
       </c>
       <c r="J92" s="3" t="n">
-        <v>0</v>
+        <v>3.497884</v>
       </c>
       <c r="K92" s="3" t="n">
-        <v>0</v>
+        <v>3.563584</v>
       </c>
       <c r="L92" s="3" t="n">
-        <v>0</v>
+        <v>3.565284</v>
       </c>
       <c r="M92" s="3" t="n">
-        <v>0</v>
+        <v>3.565284</v>
       </c>
     </row>
     <row r="93">
@@ -7804,7 +7804,11 @@
           <t>Share-based payments reserve (Note 7)</t>
         </is>
       </c>
-      <c r="D16" t="inlineStr"/>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E16" t="inlineStr">
         <is>
           <t>-</t>
@@ -8686,7 +8690,11 @@
           <t>Share-based payments reserve (Note 8)</t>
         </is>
       </c>
-      <c r="D29" t="inlineStr"/>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E29" t="inlineStr">
         <is>
           <t>-</t>
@@ -9474,7 +9482,11 @@
           <t>Share-based payments reserve</t>
         </is>
       </c>
-      <c r="D40" t="inlineStr"/>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E40" t="inlineStr">
         <is>
           <t>-</t>

--- a/output/pdf_financials_xlsx/GNG.xlsx
+++ b/output/pdf_financials_xlsx/GNG.xlsx
@@ -911,10 +911,10 @@
         </is>
       </c>
       <c r="B12" s="3" t="n">
-        <v>0</v>
+        <v>0.009043000000000001</v>
       </c>
       <c r="C12" s="3" t="n">
-        <v>0</v>
+        <v>0.004156</v>
       </c>
       <c r="D12" s="3" t="n">
         <v>0</v>
@@ -934,16 +934,16 @@
         </is>
       </c>
       <c r="I12" s="3" t="n">
-        <v>0</v>
+        <v>0.016547</v>
       </c>
       <c r="J12" s="3" t="n">
-        <v>0</v>
+        <v>0.008926</v>
       </c>
       <c r="K12" s="3" t="n">
-        <v>0</v>
+        <v>0.004095</v>
       </c>
       <c r="L12" s="3" t="n">
-        <v>0</v>
+        <v>0.012264</v>
       </c>
       <c r="M12" s="1" t="inlineStr">
         <is>
@@ -1668,10 +1668,10 @@
         </is>
       </c>
       <c r="B27" s="3" t="n">
-        <v>-2.930155</v>
+        <v>-2.939198</v>
       </c>
       <c r="C27" s="3" t="n">
-        <v>-3.548518</v>
+        <v>-3.552674</v>
       </c>
       <c r="D27" s="3" t="n">
         <v>-0.575408</v>
@@ -1691,16 +1691,16 @@
         </is>
       </c>
       <c r="I27" s="3" t="n">
-        <v>-1.059894</v>
+        <v>-1.076441</v>
       </c>
       <c r="J27" s="3" t="n">
-        <v>-0.989982</v>
+        <v>-0.998908</v>
       </c>
       <c r="K27" s="3" t="n">
-        <v>-0.5965859999999999</v>
+        <v>-0.600681</v>
       </c>
       <c r="L27" s="3" t="n">
-        <v>-0.552608</v>
+        <v>-0.564872</v>
       </c>
       <c r="M27" s="1" t="inlineStr">
         <is>
@@ -1762,10 +1762,10 @@
         </is>
       </c>
       <c r="B29" s="3" t="n">
-        <v>-2.930155</v>
+        <v>-2.939198</v>
       </c>
       <c r="C29" s="3" t="n">
-        <v>-3.548518</v>
+        <v>-3.552674</v>
       </c>
       <c r="D29" s="3" t="n">
         <v>-0.575408</v>
@@ -1785,16 +1785,16 @@
         </is>
       </c>
       <c r="I29" s="3" t="n">
-        <v>-1.059894</v>
+        <v>-1.076441</v>
       </c>
       <c r="J29" s="3" t="n">
-        <v>-0.989982</v>
+        <v>-0.998908</v>
       </c>
       <c r="K29" s="3" t="n">
-        <v>-0.5965859999999999</v>
+        <v>-0.600681</v>
       </c>
       <c r="L29" s="3" t="n">
-        <v>-0.552608</v>
+        <v>-0.564872</v>
       </c>
       <c r="M29" s="1" t="inlineStr">
         <is>
@@ -2002,37 +2002,37 @@
         </is>
       </c>
       <c r="C34" s="3" t="n">
-        <v>0</v>
+        <v>0.105407</v>
       </c>
       <c r="D34" s="3" t="n">
-        <v>0</v>
+        <v>0.099235</v>
       </c>
       <c r="E34" s="3" t="n">
-        <v>0</v>
+        <v>0.05788</v>
       </c>
       <c r="F34" s="3" t="n">
-        <v>0</v>
+        <v>0.068123</v>
       </c>
       <c r="G34" s="3" t="n">
-        <v>0</v>
+        <v>0.063641</v>
       </c>
       <c r="H34" s="3" t="n">
-        <v>0</v>
+        <v>0.35574</v>
       </c>
       <c r="I34" s="3" t="n">
-        <v>0</v>
+        <v>2.251482</v>
       </c>
       <c r="J34" s="3" t="n">
-        <v>0</v>
+        <v>0.07487199999999999</v>
       </c>
       <c r="K34" s="3" t="n">
-        <v>0</v>
+        <v>0.137535</v>
       </c>
       <c r="L34" s="3" t="n">
-        <v>0</v>
+        <v>0.131703</v>
       </c>
       <c r="M34" s="3" t="n">
-        <v>0</v>
+        <v>0.002831</v>
       </c>
     </row>
     <row r="35">
@@ -2092,37 +2092,37 @@
         </is>
       </c>
       <c r="C36" s="3" t="n">
-        <v>0.01275</v>
+        <v>0.118157</v>
       </c>
       <c r="D36" s="3" t="n">
-        <v>0.010625</v>
+        <v>0.10986</v>
       </c>
       <c r="E36" s="3" t="n">
-        <v>0</v>
+        <v>0.05788</v>
       </c>
       <c r="F36" s="3" t="n">
-        <v>0</v>
+        <v>0.068123</v>
       </c>
       <c r="G36" s="3" t="n">
-        <v>0</v>
+        <v>0.063641</v>
       </c>
       <c r="H36" s="3" t="n">
-        <v>1.013321</v>
+        <v>1.369061</v>
       </c>
       <c r="I36" s="3" t="n">
-        <v>0.779024</v>
+        <v>3.030506</v>
       </c>
       <c r="J36" s="3" t="n">
-        <v>1.704145</v>
+        <v>1.779017</v>
       </c>
       <c r="K36" s="3" t="n">
-        <v>0.8575159999999999</v>
+        <v>0.995051</v>
       </c>
       <c r="L36" s="3" t="n">
-        <v>0.315143</v>
+        <v>0.446846</v>
       </c>
       <c r="M36" s="3" t="n">
-        <v>0</v>
+        <v>0.002831</v>
       </c>
     </row>
     <row r="37">
@@ -2632,37 +2632,37 @@
         </is>
       </c>
       <c r="C48" s="3" t="n">
-        <v>0.170739</v>
+        <v>0.065332</v>
       </c>
       <c r="D48" s="3" t="n">
-        <v>0.151715</v>
+        <v>0.05248</v>
       </c>
       <c r="E48" s="3" t="n">
-        <v>0.099124</v>
+        <v>0.041244</v>
       </c>
       <c r="F48" s="3" t="n">
-        <v>0.107332</v>
+        <v>0.039209</v>
       </c>
       <c r="G48" s="3" t="n">
-        <v>0.06995899999999999</v>
+        <v>0.006318</v>
       </c>
       <c r="H48" s="3" t="n">
-        <v>0.358107</v>
+        <v>0.002367</v>
       </c>
       <c r="I48" s="3" t="n">
-        <v>2.297212</v>
+        <v>0.04573</v>
       </c>
       <c r="J48" s="3" t="n">
-        <v>0.113497</v>
+        <v>0.038625</v>
       </c>
       <c r="K48" s="3" t="n">
-        <v>0.171747</v>
+        <v>0.034212</v>
       </c>
       <c r="L48" s="3" t="n">
-        <v>0.134894</v>
+        <v>0.003191</v>
       </c>
       <c r="M48" s="3" t="n">
-        <v>0.149804</v>
+        <v>0.146973</v>
       </c>
     </row>
     <row r="49">
@@ -6828,7 +6828,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -17410,7 +17410,7 @@
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E148" t="inlineStr">
@@ -20342,7 +20342,7 @@
       </c>
       <c r="D188" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E188" s="5" t="n">

--- a/output/pdf_financials_xlsx/GNG.xlsx
+++ b/output/pdf_financials_xlsx/GNG.xlsx
@@ -5570,7 +5570,7 @@
         <v>0</v>
       </c>
       <c r="C112" s="3" t="n">
-        <v>0</v>
+        <v>0.004615</v>
       </c>
       <c r="D112" s="3" t="n">
         <v>0</v>
@@ -16290,7 +16290,11 @@
           <t>Proceeds on sale of property and equipment</t>
         </is>
       </c>
-      <c r="D132" t="inlineStr"/>
+      <c r="D132" t="inlineStr">
+        <is>
+          <t>SaleOfPPE</t>
+        </is>
+      </c>
       <c r="E132" t="inlineStr">
         <is>
           <t>-</t>
